--- a/resumen_woocommerce_2026-09-12.xlsx
+++ b/resumen_woocommerce_2026-09-12.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4913</v>
+        <v>4835</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -482,24 +482,24 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46242.62188657407</v>
+        <v>46204.71905092592</v>
       </c>
       <c r="D2" t="n">
-        <v>240000</v>
+        <v>260491</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>41591</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>240000</v>
+        <v>218900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4923</v>
+        <v>4836</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -507,10 +507,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46237.66237268518</v>
+        <v>46206.58997685185</v>
       </c>
       <c r="D3" t="n">
-        <v>43000</v>
+        <v>658600</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -519,12 +519,12 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>43000</v>
+        <v>658600</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4924</v>
+        <v>4837</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46237.71487268519</v>
+        <v>46206.7766550926</v>
       </c>
       <c r="D4" t="n">
-        <v>329300</v>
+        <v>685300</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -544,12 +544,12 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>329300</v>
+        <v>685300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4925</v>
+        <v>4838</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -557,24 +557,24 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46237.79278935185</v>
+        <v>46206.88664351852</v>
       </c>
       <c r="D5" t="n">
-        <v>96000</v>
+        <v>556682</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>88882</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>96000</v>
+        <v>467800</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4927</v>
+        <v>4851</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46238.99318287037</v>
+        <v>46207.66054398148</v>
       </c>
       <c r="D6" t="n">
-        <v>170600</v>
+        <v>251000</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -594,12 +594,12 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>170600</v>
+        <v>251000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4929</v>
+        <v>4852</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46239.81222222222</v>
+        <v>46209.7491087963</v>
       </c>
       <c r="D7" t="n">
-        <v>15504</v>
+        <v>240000</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -619,12 +619,12 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>15504</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4931</v>
+        <v>4854</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46239.81469907407</v>
+        <v>46209.99140046296</v>
       </c>
       <c r="D8" t="n">
-        <v>136500</v>
+        <v>42800</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -644,12 +644,12 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>136500</v>
+        <v>42800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4932</v>
+        <v>4856</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46239.82112268519</v>
+        <v>46210.96150462963</v>
       </c>
       <c r="D9" t="n">
-        <v>72000</v>
+        <v>1562100</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -669,12 +669,12 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>72000</v>
+        <v>1562100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4936</v>
+        <v>4857</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46241.04262731481</v>
+        <v>46211.82885416667</v>
       </c>
       <c r="D10" t="n">
-        <v>240400</v>
+        <v>329000</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -694,12 +694,12 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>240400</v>
+        <v>329000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4937</v>
+        <v>4858</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -707,19 +707,1069 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46242.91528935185</v>
+        <v>46211.85099537037</v>
       </c>
       <c r="D11" t="n">
-        <v>77297</v>
+        <v>179690</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>28690</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>77297</v>
+        <v>151000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4861</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>46212.16304398148</v>
+      </c>
+      <c r="D12" t="n">
+        <v>76400</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>76400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4862</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>46212.16641203704</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29400</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>29400</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4863</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46212.16824074074</v>
+      </c>
+      <c r="D14" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4867</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46212.63619212963</v>
+      </c>
+      <c r="D15" t="n">
+        <v>625000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4868</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46213.17684027777</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4869</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46213.17868055555</v>
+      </c>
+      <c r="D17" t="n">
+        <v>62400</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>62400</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4870</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46213.89826388889</v>
+      </c>
+      <c r="D18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4871</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46213.96106481482</v>
+      </c>
+      <c r="D19" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4872</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46214.63101851852</v>
+      </c>
+      <c r="D20" t="n">
+        <v>672000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>672000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4873</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46215.1359837963</v>
+      </c>
+      <c r="D21" t="n">
+        <v>56644</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9044</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>47600</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4874</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46217.67444444444</v>
+      </c>
+      <c r="D22" t="n">
+        <v>54200</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>54200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4876</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46217.97049768519</v>
+      </c>
+      <c r="D23" t="n">
+        <v>82200</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>82200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4878</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46217.97313657407</v>
+      </c>
+      <c r="D24" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4879</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46218.00800925926</v>
+      </c>
+      <c r="D25" t="n">
+        <v>18600</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>18600</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4880</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46218.65085648148</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2426000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2426000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4881</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46220.65711805555</v>
+      </c>
+      <c r="D27" t="n">
+        <v>317200</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>317200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4884</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46220.80984953704</v>
+      </c>
+      <c r="D28" t="n">
+        <v>88700</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>88700</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4885</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46221.05619212963</v>
+      </c>
+      <c r="D29" t="n">
+        <v>183260</v>
+      </c>
+      <c r="E29" t="n">
+        <v>29260</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>154000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4887</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46221.95284722222</v>
+      </c>
+      <c r="D30" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4888</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46224.62450231481</v>
+      </c>
+      <c r="D31" t="n">
+        <v>223400</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>223400</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4890</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46225.0194675926</v>
+      </c>
+      <c r="D32" t="n">
+        <v>709240</v>
+      </c>
+      <c r="E32" t="n">
+        <v>113240</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>596000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>4893</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46225.13513888889</v>
+      </c>
+      <c r="D33" t="n">
+        <v>43000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>4894</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46225.14269675926</v>
+      </c>
+      <c r="D34" t="n">
+        <v>18919</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>18919</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4895</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46225.86041666667</v>
+      </c>
+      <c r="D35" t="n">
+        <v>172669</v>
+      </c>
+      <c r="E35" t="n">
+        <v>27569</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>145100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4897</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46226.66626157407</v>
+      </c>
+      <c r="D36" t="n">
+        <v>383900</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>383900</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4898</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46226.74449074074</v>
+      </c>
+      <c r="D37" t="n">
+        <v>156000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4899</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46226.86318287037</v>
+      </c>
+      <c r="D38" t="n">
+        <v>57600</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>57600</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4901</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46226.86822916667</v>
+      </c>
+      <c r="D39" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4902</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46226.87037037037</v>
+      </c>
+      <c r="D40" t="n">
+        <v>74600</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>74600</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4903</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46226.87275462963</v>
+      </c>
+      <c r="D41" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4904</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>46226.93824074074</v>
+      </c>
+      <c r="D42" t="n">
+        <v>47838</v>
+      </c>
+      <c r="E42" t="n">
+        <v>7638</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>40200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4906</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46230.61726851852</v>
+      </c>
+      <c r="D43" t="n">
+        <v>105700</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>105700</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4907</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>46230.85891203704</v>
+      </c>
+      <c r="D44" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4908</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46230.8921875</v>
+      </c>
+      <c r="D45" t="n">
+        <v>115946</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>115946</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4909</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46230.89417824074</v>
+      </c>
+      <c r="D46" t="n">
+        <v>89000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>89000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4910</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46230.89789351852</v>
+      </c>
+      <c r="D47" t="n">
+        <v>49500</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4911</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46231.84287037037</v>
+      </c>
+      <c r="D48" t="n">
+        <v>125400</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>125400</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4912</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46232.61981481482</v>
+      </c>
+      <c r="D49" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>73000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4914</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46232.6505787037</v>
+      </c>
+      <c r="D50" t="n">
+        <v>90200</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>90200</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4915</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46232.65491898148</v>
+      </c>
+      <c r="D51" t="n">
+        <v>43340</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>43340</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4916</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46232.66456018519</v>
+      </c>
+      <c r="D52" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4918</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46233.81182870371</v>
+      </c>
+      <c r="D53" t="n">
+        <v>374000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>374000</v>
       </c>
     </row>
   </sheetData>
@@ -733,7 +1783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,7 +1815,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4913</v>
+        <v>4835</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -773,37 +1823,37 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46242.62188657407</v>
+        <v>46204.71905092592</v>
       </c>
       <c r="D2" t="n">
-        <v>240000</v>
+        <v>260491</v>
       </c>
       <c r="E2" t="n">
-        <v>240000</v>
+        <v>218900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4922</v>
+        <v>4836</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>wc-pending</t>
+          <t>wc-completed</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46237.66002314815</v>
+        <v>46206.58997685185</v>
       </c>
       <c r="D3" t="n">
-        <v>62500</v>
+        <v>658600</v>
       </c>
       <c r="E3" t="n">
-        <v>62500</v>
+        <v>658600</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4923</v>
+        <v>4837</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -811,18 +1861,18 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46237.66237268518</v>
+        <v>46206.7766550926</v>
       </c>
       <c r="D4" t="n">
-        <v>43000</v>
+        <v>685300</v>
       </c>
       <c r="E4" t="n">
-        <v>43000</v>
+        <v>685300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4924</v>
+        <v>4838</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -830,18 +1880,18 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46237.71487268519</v>
+        <v>46206.88664351852</v>
       </c>
       <c r="D5" t="n">
-        <v>329300</v>
+        <v>556682</v>
       </c>
       <c r="E5" t="n">
-        <v>329300</v>
+        <v>467800</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4925</v>
+        <v>4851</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -849,75 +1899,75 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46237.79278935185</v>
+        <v>46207.66054398148</v>
       </c>
       <c r="D6" t="n">
-        <v>96000</v>
+        <v>251000</v>
       </c>
       <c r="E6" t="n">
-        <v>96000</v>
+        <v>251000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4926</v>
+        <v>4852</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>wc-cancelled</t>
+          <t>wc-completed</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46237.89811342592</v>
+        <v>46209.7491087963</v>
       </c>
       <c r="D7" t="n">
-        <v>847000</v>
+        <v>240000</v>
       </c>
       <c r="E7" t="n">
-        <v>847000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4927</v>
+        <v>4853</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wc-completed</t>
+          <t>wc-pending</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46238.99318287037</v>
+        <v>46209.98538194445</v>
       </c>
       <c r="D8" t="n">
-        <v>170600</v>
+        <v>144680</v>
       </c>
       <c r="E8" t="n">
-        <v>170600</v>
+        <v>144680</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4928</v>
+        <v>4854</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wc-cancelled</t>
+          <t>wc-completed</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46239.67038194444</v>
+        <v>46209.99140046296</v>
       </c>
       <c r="D9" t="n">
-        <v>223720</v>
+        <v>42800</v>
       </c>
       <c r="E9" t="n">
-        <v>188000</v>
+        <v>42800</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4929</v>
+        <v>4856</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -925,18 +1975,18 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46239.81222222222</v>
+        <v>46210.96150462963</v>
       </c>
       <c r="D10" t="n">
-        <v>15504</v>
+        <v>1562100</v>
       </c>
       <c r="E10" t="n">
-        <v>15504</v>
+        <v>1562100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4931</v>
+        <v>4857</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -944,18 +1994,18 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46239.81469907407</v>
+        <v>46211.82885416667</v>
       </c>
       <c r="D11" t="n">
-        <v>136500</v>
+        <v>329000</v>
       </c>
       <c r="E11" t="n">
-        <v>136500</v>
+        <v>329000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4932</v>
+        <v>4858</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -963,18 +2013,18 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46239.82112268519</v>
+        <v>46211.85099537037</v>
       </c>
       <c r="D12" t="n">
-        <v>72000</v>
+        <v>179690</v>
       </c>
       <c r="E12" t="n">
-        <v>72000</v>
+        <v>151000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4936</v>
+        <v>4861</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -982,18 +2032,18 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46241.04262731481</v>
+        <v>46212.16304398148</v>
       </c>
       <c r="D13" t="n">
-        <v>240400</v>
+        <v>76400</v>
       </c>
       <c r="E13" t="n">
-        <v>240400</v>
+        <v>76400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4937</v>
+        <v>4862</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1001,13 +2051,887 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46242.91528935185</v>
+        <v>46212.16641203704</v>
       </c>
       <c r="D14" t="n">
-        <v>77297</v>
+        <v>29400</v>
       </c>
       <c r="E14" t="n">
-        <v>77297</v>
+        <v>29400</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4863</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46212.16824074074</v>
+      </c>
+      <c r="D15" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4864</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>wc-cancelled</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46212.54756944445</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30702</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25800</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4867</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46212.63619212963</v>
+      </c>
+      <c r="D17" t="n">
+        <v>625000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4868</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46213.17684027777</v>
+      </c>
+      <c r="D18" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4869</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46213.17868055555</v>
+      </c>
+      <c r="D19" t="n">
+        <v>62400</v>
+      </c>
+      <c r="E19" t="n">
+        <v>62400</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4870</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46213.89826388889</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4871</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46213.96106481482</v>
+      </c>
+      <c r="D21" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4872</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46214.63101851852</v>
+      </c>
+      <c r="D22" t="n">
+        <v>672000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>672000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4873</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46215.1359837963</v>
+      </c>
+      <c r="D23" t="n">
+        <v>56644</v>
+      </c>
+      <c r="E23" t="n">
+        <v>47600</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4874</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46217.67444444444</v>
+      </c>
+      <c r="D24" t="n">
+        <v>54200</v>
+      </c>
+      <c r="E24" t="n">
+        <v>54200</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4875</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46217.73592592592</v>
+      </c>
+      <c r="D25" t="n">
+        <v>450900</v>
+      </c>
+      <c r="E25" t="n">
+        <v>450900</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4876</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46217.97049768519</v>
+      </c>
+      <c r="D26" t="n">
+        <v>82200</v>
+      </c>
+      <c r="E26" t="n">
+        <v>82200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4878</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46217.97313657407</v>
+      </c>
+      <c r="D27" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4879</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46218.00800925926</v>
+      </c>
+      <c r="D28" t="n">
+        <v>18600</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18600</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4880</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46218.65085648148</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2426000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2426000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4881</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46220.65711805555</v>
+      </c>
+      <c r="D30" t="n">
+        <v>317200</v>
+      </c>
+      <c r="E30" t="n">
+        <v>317200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4884</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46220.80984953704</v>
+      </c>
+      <c r="D31" t="n">
+        <v>88700</v>
+      </c>
+      <c r="E31" t="n">
+        <v>88700</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4885</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46221.05619212963</v>
+      </c>
+      <c r="D32" t="n">
+        <v>183260</v>
+      </c>
+      <c r="E32" t="n">
+        <v>154000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>4887</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46221.95284722222</v>
+      </c>
+      <c r="D33" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>4888</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46224.62450231481</v>
+      </c>
+      <c r="D34" t="n">
+        <v>223400</v>
+      </c>
+      <c r="E34" t="n">
+        <v>223400</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4889</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46224.86627314815</v>
+      </c>
+      <c r="D35" t="n">
+        <v>719000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>719000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4890</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46225.0194675926</v>
+      </c>
+      <c r="D36" t="n">
+        <v>709240</v>
+      </c>
+      <c r="E36" t="n">
+        <v>596000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4893</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46225.13513888889</v>
+      </c>
+      <c r="D37" t="n">
+        <v>43000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4894</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46225.14269675926</v>
+      </c>
+      <c r="D38" t="n">
+        <v>18919</v>
+      </c>
+      <c r="E38" t="n">
+        <v>18919</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4895</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46225.86041666667</v>
+      </c>
+      <c r="D39" t="n">
+        <v>172669</v>
+      </c>
+      <c r="E39" t="n">
+        <v>145100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4896</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46225.95689814815</v>
+      </c>
+      <c r="D40" t="n">
+        <v>631000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>631000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4897</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46226.66626157407</v>
+      </c>
+      <c r="D41" t="n">
+        <v>383900</v>
+      </c>
+      <c r="E41" t="n">
+        <v>383900</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4898</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>46226.74449074074</v>
+      </c>
+      <c r="D42" t="n">
+        <v>156000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4899</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46226.86318287037</v>
+      </c>
+      <c r="D43" t="n">
+        <v>57600</v>
+      </c>
+      <c r="E43" t="n">
+        <v>57600</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4901</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>46226.86822916667</v>
+      </c>
+      <c r="D44" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4902</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46226.87037037037</v>
+      </c>
+      <c r="D45" t="n">
+        <v>74600</v>
+      </c>
+      <c r="E45" t="n">
+        <v>74600</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4903</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46226.87275462963</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4904</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46226.93824074074</v>
+      </c>
+      <c r="D47" t="n">
+        <v>47838</v>
+      </c>
+      <c r="E47" t="n">
+        <v>40200</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4905</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wc-cancelled</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46227.88310185185</v>
+      </c>
+      <c r="D48" t="n">
+        <v>49742</v>
+      </c>
+      <c r="E48" t="n">
+        <v>41800</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4906</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46230.61726851852</v>
+      </c>
+      <c r="D49" t="n">
+        <v>105700</v>
+      </c>
+      <c r="E49" t="n">
+        <v>105700</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4907</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46230.85891203704</v>
+      </c>
+      <c r="D50" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4908</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46230.8921875</v>
+      </c>
+      <c r="D51" t="n">
+        <v>115946</v>
+      </c>
+      <c r="E51" t="n">
+        <v>115946</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4909</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46230.89417824074</v>
+      </c>
+      <c r="D52" t="n">
+        <v>89000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>89000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4910</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46230.89789351852</v>
+      </c>
+      <c r="D53" t="n">
+        <v>49500</v>
+      </c>
+      <c r="E53" t="n">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4911</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46231.84287037037</v>
+      </c>
+      <c r="D54" t="n">
+        <v>125400</v>
+      </c>
+      <c r="E54" t="n">
+        <v>125400</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4912</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46232.61981481482</v>
+      </c>
+      <c r="D55" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E55" t="n">
+        <v>73000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4914</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46232.6505787037</v>
+      </c>
+      <c r="D56" t="n">
+        <v>90200</v>
+      </c>
+      <c r="E56" t="n">
+        <v>90200</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4915</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46232.65491898148</v>
+      </c>
+      <c r="D57" t="n">
+        <v>43340</v>
+      </c>
+      <c r="E57" t="n">
+        <v>43340</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4916</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46232.66456018519</v>
+      </c>
+      <c r="D58" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4917</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46232.81538194444</v>
+      </c>
+      <c r="D59" t="n">
+        <v>179000</v>
+      </c>
+      <c r="E59" t="n">
+        <v>179000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4918</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46233.81182870371</v>
+      </c>
+      <c r="D60" t="n">
+        <v>374000</v>
+      </c>
+      <c r="E60" t="n">
+        <v>374000</v>
       </c>
     </row>
   </sheetData>
@@ -1021,7 +2945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,493 +2995,1613 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="E2" t="n">
-        <v>316097</v>
+        <v>1148265</v>
       </c>
       <c r="F2" t="n">
-        <v>316097</v>
+        <v>1168215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3005</v>
+        <v>4826</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cabeza de Contra Angulo NSK-Pieza de Mano Contraangulo NSK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CCANSK</t>
-        </is>
-      </c>
+          <t>Lampara Led 4 focos</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>166000</v>
+        <v>1030000</v>
       </c>
       <c r="F3" t="n">
-        <v>166000</v>
+        <v>1030000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manguera 1/4 Amarilla X metro</t>
+          <t>Pedal Neumatico Odontologico</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MN14A</t>
+          <t>PMN</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>156400</v>
+        <v>978000</v>
       </c>
       <c r="F4" t="n">
-        <v>156400</v>
+        <v>978000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>373</v>
+        <v>352</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Holder Sencillo Tipo Huevo</t>
+          <t>Valvula Reguladora</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HSTH</t>
+          <t>VR</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E5" t="n">
-        <v>125004</v>
+        <v>684500</v>
       </c>
       <c r="F5" t="n">
-        <v>125004</v>
+        <v>684500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1096</v>
+        <v>1017</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Acople Borden Chino- Acople Borden Importado</t>
+          <t>Rollo 50mts Manguera Nacional 1/4 Azul</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ACBC</t>
+          <t>RMN14</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>98000</v>
+        <v>525000</v>
       </c>
       <c r="F6" t="n">
-        <v>98000</v>
+        <v>558250</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Valvula On/Off</t>
+          <t>Válvula Piloto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VOF</t>
+          <t>VP</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>88000</v>
+        <v>451300</v>
       </c>
       <c r="F7" t="n">
-        <v>88000</v>
+        <v>459128</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2906</v>
+        <v>356</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Manguera Pieza de Mano 2 Orificios</t>
+          <t>Valvula Cambia Vias</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MPM2</t>
+          <t>VCV</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>85200</v>
+        <v>416000</v>
       </c>
       <c r="F8" t="n">
-        <v>85200</v>
+        <v>416000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2900</v>
+        <v>1096</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pedal Unidad Dental- Pedal Odontologico Importado</t>
+          <t>Acople Borden Chino- Acople Borden Importado</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PUDI</t>
+          <t>ACBC</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>72000</v>
+        <v>372000</v>
       </c>
       <c r="F9" t="n">
-        <v>72000</v>
+        <v>374736</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>353</v>
+        <v>1016</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeringa triple</t>
+          <t>Rollo 50mts Manguera Nacional 1/4 Amarilla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>RMN14A</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>60000</v>
+        <v>362000</v>
       </c>
       <c r="F10" t="n">
-        <v>60000</v>
+        <v>395250</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cambia Fresas Estandar</t>
+          <t>Jeringa triple</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CFE</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>48000</v>
+        <v>328000</v>
       </c>
       <c r="F11" t="n">
-        <v>48000</v>
+        <v>328000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>391</v>
+        <v>1870</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Manguera 1/4 Azul X metro</t>
+          <t>Reguladora de aire con filtro, Valvula Reguladora de Aire o Filtro Regulador de aire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MN14</t>
+          <t>VRA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>38000</v>
+        <v>292000</v>
       </c>
       <c r="F12" t="n">
-        <v>38000</v>
+        <v>292000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3332</v>
+        <v>379</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tanque reservatorio Blanco 1 litro sin Tapa</t>
+          <t>Valvula On/Off</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TST12</t>
+          <t>VOF</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>32000</v>
+        <v>292000</v>
       </c>
       <c r="F13" t="n">
-        <v>32000</v>
+        <v>292000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3301</v>
+        <v>2143</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reguladora de agua y aire sin filtro</t>
+          <t>Valvula de Succion de Baja/Boquilla de Baja Quirurgica importada</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RAV</t>
+          <t>BAI</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>28000</v>
+        <v>279000</v>
       </c>
       <c r="F14" t="n">
-        <v>28000</v>
+        <v>283370</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3330</v>
+        <v>2900</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tanque reservatorio Blanco 1 litro con Tapa</t>
+          <t>Pedal Unidad Dental- Pedal Odontologico Importado</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TA12</t>
+          <t>PUDI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>27000</v>
+        <v>263000</v>
       </c>
       <c r="F15" t="n">
-        <v>27000</v>
+        <v>274020</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3168</v>
+        <v>3330</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Holder Sencillo o Holder con Pie de Amigo Blanco</t>
+          <t>Tanque reservatorio Blanco 1 litro con Tapa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HSB</t>
+          <t>TA12</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>20400</v>
+        <v>255000</v>
       </c>
       <c r="F16" t="n">
-        <v>20400</v>
+        <v>279225</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Valvula Reguladora</t>
+          <t>Filtro de Agua para Unidad Odontologica</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VR</t>
+          <t>FA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>16500</v>
+        <v>236000</v>
       </c>
       <c r="F17" t="n">
-        <v>16500</v>
+        <v>267920</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>390</v>
+        <v>4844</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Manguera Coraza 3/4 X metro</t>
+          <t>Escupidera cristal o Taza Dental de Cristal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MC34</t>
+          <t>ECD</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>16000</v>
+        <v>235000</v>
       </c>
       <c r="F18" t="n">
-        <v>16000</v>
+        <v>258750</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manguera Jeringa X metro</t>
+          <t>Tee Racor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MJT</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>165</v>
       </c>
       <c r="E19" t="n">
-        <v>9800</v>
+        <v>232500</v>
       </c>
       <c r="F19" t="n">
-        <v>9800</v>
+        <v>235350</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fitin Racor 1/4</t>
+          <t>Manguera 1/4 Azul X metro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>F14</t>
+          <t>MN14</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
-        <v>8000</v>
+        <v>212500</v>
       </c>
       <c r="F20" t="n">
-        <v>8000</v>
+        <v>224755</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>378</v>
+        <v>1880</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manguera Eyector Baja X metro</t>
+          <t>Punta Caucho Set Eyector o Punta Boquilla de Eyector X 5 unidades el juego</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MEB</t>
+          <t>KPC</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>7200</v>
+        <v>210000</v>
       </c>
       <c r="F21" t="n">
-        <v>7200</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>397</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fitin Racor 1/4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>F14</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>245</v>
+      </c>
+      <c r="E22" t="n">
+        <v>198500</v>
+      </c>
+      <c r="F22" t="n">
+        <v>200210</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>373</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Holder Sencillo Tipo Huevo</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HSTH</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" t="n">
+        <v>193100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>196786</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>371</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Set Eyector o Boquilla eyectora</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>32</v>
+      </c>
+      <c r="E24" t="n">
+        <v>179900</v>
+      </c>
+      <c r="F24" t="n">
+        <v>191566</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rollo 50mts Manguera Eyector de Baja</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RMEB</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>174000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>174000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>405</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Racor Union Mixta 1/4 a 1/8</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>UM48</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D26" t="n">
+        <v>128</v>
+      </c>
+      <c r="E26" t="n">
+        <v>172300</v>
+      </c>
+      <c r="F26" t="n">
+        <v>173725</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>390</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Manguera Coraza 3/4 X metro</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MC34</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" t="n">
+        <v>170700</v>
+      </c>
+      <c r="F27" t="n">
+        <v>179877</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2268</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Valvula de Succion de Alta importada/Boquilla de Alta Importada</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BBI</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>161000</v>
+      </c>
+      <c r="F28" t="n">
+        <v>161000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>398</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fitin Racor 1/8</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>F18</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>201</v>
+      </c>
+      <c r="E29" t="n">
+        <v>160900</v>
+      </c>
+      <c r="F29" t="n">
+        <v>161071</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>363</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bandeja Auxiliar Cavitron Dental</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BAC</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>159000</v>
+      </c>
+      <c r="F30" t="n">
+        <v>159000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>392</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Manguera Pieza Mano X metro</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MPM</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" t="n">
+        <v>148800</v>
+      </c>
+      <c r="F31" t="n">
+        <v>148800</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3332</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tanque reservatorio Blanco 1 litro sin Tapa</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TST12</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>127900</v>
+      </c>
+      <c r="F32" t="n">
+        <v>142625</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3219</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Valvula Ventury Baja Bronce</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VVB2</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" t="n">
+        <v>119000</v>
+      </c>
+      <c r="F33" t="n">
+        <v>125460</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2906</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Manguera Pieza de Mano 2 Orificios</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MPM2</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>16</v>
+      </c>
+      <c r="E34" t="n">
+        <v>113000</v>
+      </c>
+      <c r="F34" t="n">
+        <v>119080</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Convertidor de Acople Midwest a Borden</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CAMB</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>112200</v>
+      </c>
+      <c r="F35" t="n">
+        <v>118660</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>389</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Manguera 1/4 Amarilla X metro</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MN14A</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>29</v>
+      </c>
+      <c r="E36" t="n">
+        <v>99300</v>
+      </c>
+      <c r="F36" t="n">
+        <v>102815</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>364</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Canastilla o Rejilla Escupidera</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>RE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>33</v>
+      </c>
+      <c r="E37" t="n">
+        <v>95140</v>
+      </c>
+      <c r="F37" t="n">
+        <v>95140</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Canastilla o Rejilla con tapa Para Escupidera Unidad Odontológica</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>17</v>
+      </c>
+      <c r="E38" t="n">
+        <v>90500</v>
+      </c>
+      <c r="F38" t="n">
+        <v>99791</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2884</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Valvula Ventury de Alta Succion de Bronce</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VVAN</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>89500</v>
+      </c>
+      <c r="F39" t="n">
+        <v>95390</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4860</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tanque pequeño 0.8 blanco</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>88500</v>
+      </c>
+      <c r="F40" t="n">
+        <v>102465</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Manguera Nacional Azul de 1/8 X Metro</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>52</v>
+      </c>
+      <c r="E41" t="n">
+        <v>85000</v>
+      </c>
+      <c r="F41" t="n">
+        <v>91270</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>394</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Acople Cavitron Macho</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>84000</v>
+      </c>
+      <c r="F42" t="n">
+        <v>87230</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rollo 50 mts Manguera de 1/8 Azul</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>RM18</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F43" t="n">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rollo 50mts Manguera Nacional 1/8 Amarilla</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>RM18A</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>77000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>378</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Manguera Eyector Baja X metro</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MEB</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>39</v>
+      </c>
+      <c r="E45" t="n">
+        <v>75600</v>
+      </c>
+      <c r="F45" t="n">
+        <v>76056</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>417</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Manguera Jeringa X metro</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MJT</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>16</v>
+      </c>
+      <c r="E46" t="n">
+        <v>71400</v>
+      </c>
+      <c r="F46" t="n">
+        <v>75124</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Manguera Nacional Amarilla 1/8 X Metro</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MA18</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>40</v>
+      </c>
+      <c r="E47" t="n">
+        <v>66000</v>
+      </c>
+      <c r="F47" t="n">
+        <v>75310</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1742</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Acople Rapido Y o Union Triple Rapida Plastica</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UTRP</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>35</v>
+      </c>
+      <c r="E48" t="n">
+        <v>63000</v>
+      </c>
+      <c r="F48" t="n">
+        <v>64710</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3161</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Conector Rapido 1/4 de Dos Salidas: Union Doble Plástica</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UDRP</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>32</v>
+      </c>
+      <c r="E49" t="n">
+        <v>57600</v>
+      </c>
+      <c r="F49" t="n">
+        <v>59310</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3301</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Reguladora de agua y aire sin filtro</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>RAV</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>2</v>
       </c>
-      <c r="E22" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F22" t="n">
-        <v>3000</v>
+      <c r="E50" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4755</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Filtro para compresor</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FC</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>54800</v>
+      </c>
+      <c r="F51" t="n">
+        <v>54800</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>368</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Holder Sencillo o Holder con Pie de Amigo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HS</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11</v>
+      </c>
+      <c r="E52" t="n">
+        <v>53400</v>
+      </c>
+      <c r="F52" t="n">
+        <v>53400</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>403</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Racor Union 1/4 a 1/4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>U44</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>37</v>
+      </c>
+      <c r="E53" t="n">
+        <v>53300</v>
+      </c>
+      <c r="F53" t="n">
+        <v>54725</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>382</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Buje Escupidera chino</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>KBEC</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>29000</v>
+      </c>
+      <c r="F54" t="n">
+        <v>34510</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>419</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Paquete Abrazaderas o Paquete de Conector Adaptador</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PA14</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>27800</v>
+      </c>
+      <c r="F55" t="n">
+        <v>30004</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bombillo Halogeno o Lampara Halogena</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BPUH3</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F56" t="n">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3060</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Acople Rapido Tee-Tee Universal Rápida-Tee Rápida Neumática</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ART</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13</v>
+      </c>
+      <c r="E57" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F57" t="n">
+        <v>26710</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>395</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Racor Cruz de cuatro entradas de racor de 1/4 o 1/8</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" t="n">
+        <v>22500</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23925</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>367</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Holder Plano</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
+      </c>
+      <c r="E59" t="n">
+        <v>22200</v>
+      </c>
+      <c r="F59" t="n">
+        <v>22200</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>384</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Racor B3</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F60" t="n">
+        <v>19906</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>377</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Empaque para Pieza de Mano</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EPM</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>7</v>
+      </c>
+      <c r="E61" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F61" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>360</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Valvula Ventury Baja De Nylon</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VVBN</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>17800</v>
+      </c>
+      <c r="F62" t="n">
+        <v>17800</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>388</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Manguera Eyector Alta X metro</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MEA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12</v>
+      </c>
+      <c r="E63" t="n">
+        <v>17600</v>
+      </c>
+      <c r="F63" t="n">
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>393</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Acople Cavitron Hembra</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ACH</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>17000</v>
+      </c>
+      <c r="F64" t="n">
+        <v>20230</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>404</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Racor Union 1/8 a 1/8</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>U88</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>12</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16800</v>
+      </c>
+      <c r="F65" t="n">
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2568</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Calis para Escupidera o Acople para Unidades Nacionales</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CAUN</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>12500</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>387</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Manguera Pedal X Metro</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MP</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>402</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Racor Tapon Fitin</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TAP</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F68" t="n">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Racor de Bronce Codo Macho</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1904</v>
       </c>
     </row>
   </sheetData>
@@ -1571,7 +4615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,7 +4657,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4913</v>
+        <v>4835</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1621,16 +4665,16 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>46242.62188657407</v>
+        <v>46204.71905092592</v>
       </c>
       <c r="D2" t="n">
-        <v>240000</v>
+        <v>260491</v>
       </c>
       <c r="E2" t="n">
-        <v>240000</v>
+        <v>218900</v>
       </c>
       <c r="F2" t="n">
-        <v>240000</v>
+        <v>218900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1638,24 +4682,24 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4922</v>
+        <v>4836</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>wc-pending</t>
+          <t>wc-completed</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>46237.66002314815</v>
+        <v>46206.58997685185</v>
       </c>
       <c r="D3" t="n">
-        <v>62500</v>
+        <v>658600</v>
       </c>
       <c r="E3" t="n">
-        <v>62500</v>
+        <v>658600</v>
       </c>
       <c r="F3" t="n">
-        <v>62500</v>
+        <v>658600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1663,7 +4707,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4923</v>
+        <v>4837</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1671,16 +4715,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>46237.66237268518</v>
+        <v>46206.7766550926</v>
       </c>
       <c r="D4" t="n">
-        <v>43000</v>
+        <v>685300</v>
       </c>
       <c r="E4" t="n">
-        <v>43000</v>
+        <v>685300</v>
       </c>
       <c r="F4" t="n">
-        <v>43000</v>
+        <v>685300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1688,7 +4732,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4924</v>
+        <v>4838</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1696,16 +4740,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>46237.71487268519</v>
+        <v>46206.88664351852</v>
       </c>
       <c r="D5" t="n">
-        <v>329300</v>
+        <v>556682</v>
       </c>
       <c r="E5" t="n">
-        <v>329300</v>
+        <v>467800</v>
       </c>
       <c r="F5" t="n">
-        <v>329300</v>
+        <v>467800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1713,7 +4757,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4925</v>
+        <v>4851</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1721,16 +4765,16 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>46237.79278935185</v>
+        <v>46207.66054398148</v>
       </c>
       <c r="D6" t="n">
-        <v>96000</v>
+        <v>251000</v>
       </c>
       <c r="E6" t="n">
-        <v>96000</v>
+        <v>251000</v>
       </c>
       <c r="F6" t="n">
-        <v>96000</v>
+        <v>251000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1738,24 +4782,24 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4926</v>
+        <v>4852</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>wc-cancelled</t>
+          <t>wc-completed</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>46237.89811342592</v>
+        <v>46209.7491087963</v>
       </c>
       <c r="D7" t="n">
-        <v>847000</v>
+        <v>240000</v>
       </c>
       <c r="E7" t="n">
-        <v>847000</v>
+        <v>240000</v>
       </c>
       <c r="F7" t="n">
-        <v>847000</v>
+        <v>240000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1763,24 +4807,24 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4927</v>
+        <v>4853</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>wc-completed</t>
+          <t>wc-pending</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>46238.99318287037</v>
+        <v>46209.98538194445</v>
       </c>
       <c r="D8" t="n">
-        <v>170600</v>
+        <v>144680</v>
       </c>
       <c r="E8" t="n">
-        <v>170600</v>
+        <v>144680</v>
       </c>
       <c r="F8" t="n">
-        <v>170600</v>
+        <v>144680</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1788,24 +4832,24 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4928</v>
+        <v>4854</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wc-cancelled</t>
+          <t>wc-completed</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>46239.67038194444</v>
+        <v>46209.99140046296</v>
       </c>
       <c r="D9" t="n">
-        <v>223720</v>
+        <v>42800</v>
       </c>
       <c r="E9" t="n">
-        <v>188000</v>
+        <v>42800</v>
       </c>
       <c r="F9" t="n">
-        <v>188000</v>
+        <v>42800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1813,7 +4857,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4929</v>
+        <v>4856</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1821,16 +4865,16 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>46239.81222222222</v>
+        <v>46210.96150462963</v>
       </c>
       <c r="D10" t="n">
-        <v>15504</v>
+        <v>1562100</v>
       </c>
       <c r="E10" t="n">
-        <v>15504</v>
+        <v>1562100</v>
       </c>
       <c r="F10" t="n">
-        <v>15504</v>
+        <v>1562100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -1838,7 +4882,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4931</v>
+        <v>4857</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1846,16 +4890,16 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>46239.81469907407</v>
+        <v>46211.82885416667</v>
       </c>
       <c r="D11" t="n">
-        <v>136500</v>
+        <v>329000</v>
       </c>
       <c r="E11" t="n">
-        <v>136500</v>
+        <v>329000</v>
       </c>
       <c r="F11" t="n">
-        <v>136500</v>
+        <v>329000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1863,7 +4907,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4932</v>
+        <v>4858</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1871,16 +4915,16 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>46239.82112268519</v>
+        <v>46211.85099537037</v>
       </c>
       <c r="D12" t="n">
-        <v>72000</v>
+        <v>179690</v>
       </c>
       <c r="E12" t="n">
-        <v>72000</v>
+        <v>151000</v>
       </c>
       <c r="F12" t="n">
-        <v>72000</v>
+        <v>151000</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1888,7 +4932,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4936</v>
+        <v>4861</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1896,16 +4940,16 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46241.04262731481</v>
+        <v>46212.16304398148</v>
       </c>
       <c r="D13" t="n">
-        <v>240400</v>
+        <v>76400</v>
       </c>
       <c r="E13" t="n">
-        <v>240400</v>
+        <v>76400</v>
       </c>
       <c r="F13" t="n">
-        <v>240400</v>
+        <v>76400</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1913,7 +4957,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4937</v>
+        <v>4862</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1921,18 +4965,1168 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46242.91528935185</v>
+        <v>46212.16641203704</v>
       </c>
       <c r="D14" t="n">
-        <v>77297</v>
+        <v>29400</v>
       </c>
       <c r="E14" t="n">
-        <v>77297</v>
+        <v>29400</v>
       </c>
       <c r="F14" t="n">
-        <v>77297</v>
+        <v>29400</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>4863</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>46212.16824074074</v>
+      </c>
+      <c r="D15" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>220000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>220000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4864</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>wc-cancelled</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>46212.54756944445</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30702</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25800</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25800</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4867</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>46212.63619212963</v>
+      </c>
+      <c r="D17" t="n">
+        <v>625000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>625000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>625000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4868</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46213.17684027777</v>
+      </c>
+      <c r="D18" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>26000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4869</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46213.17868055555</v>
+      </c>
+      <c r="D19" t="n">
+        <v>62400</v>
+      </c>
+      <c r="E19" t="n">
+        <v>62400</v>
+      </c>
+      <c r="F19" t="n">
+        <v>62400</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4870</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46213.89826388889</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4871</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46213.96106481482</v>
+      </c>
+      <c r="D21" t="n">
+        <v>52000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>52000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>4872</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46214.63101851852</v>
+      </c>
+      <c r="D22" t="n">
+        <v>672000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>672000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>672000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>4873</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46215.1359837963</v>
+      </c>
+      <c r="D23" t="n">
+        <v>56644</v>
+      </c>
+      <c r="E23" t="n">
+        <v>47600</v>
+      </c>
+      <c r="F23" t="n">
+        <v>47600</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>4874</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46217.67444444444</v>
+      </c>
+      <c r="D24" t="n">
+        <v>54200</v>
+      </c>
+      <c r="E24" t="n">
+        <v>54200</v>
+      </c>
+      <c r="F24" t="n">
+        <v>54200</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4875</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46217.73592592592</v>
+      </c>
+      <c r="D25" t="n">
+        <v>450900</v>
+      </c>
+      <c r="E25" t="n">
+        <v>450900</v>
+      </c>
+      <c r="F25" t="n">
+        <v>450900</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>4876</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46217.97049768519</v>
+      </c>
+      <c r="D26" t="n">
+        <v>82200</v>
+      </c>
+      <c r="E26" t="n">
+        <v>82200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>82200</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>4878</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46217.97313657407</v>
+      </c>
+      <c r="D27" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4879</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46218.00800925926</v>
+      </c>
+      <c r="D28" t="n">
+        <v>18600</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18600</v>
+      </c>
+      <c r="F28" t="n">
+        <v>18600</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4880</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46218.65085648148</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2426000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2426000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2426000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4881</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46220.65711805555</v>
+      </c>
+      <c r="D30" t="n">
+        <v>317200</v>
+      </c>
+      <c r="E30" t="n">
+        <v>317200</v>
+      </c>
+      <c r="F30" t="n">
+        <v>317200</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4884</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46220.80984953704</v>
+      </c>
+      <c r="D31" t="n">
+        <v>88700</v>
+      </c>
+      <c r="E31" t="n">
+        <v>88700</v>
+      </c>
+      <c r="F31" t="n">
+        <v>88700</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>4885</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46221.05619212963</v>
+      </c>
+      <c r="D32" t="n">
+        <v>183260</v>
+      </c>
+      <c r="E32" t="n">
+        <v>154000</v>
+      </c>
+      <c r="F32" t="n">
+        <v>154000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>4887</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>46221.95284722222</v>
+      </c>
+      <c r="D33" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>92000</v>
+      </c>
+      <c r="F33" t="n">
+        <v>92000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>4888</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46224.62450231481</v>
+      </c>
+      <c r="D34" t="n">
+        <v>223400</v>
+      </c>
+      <c r="E34" t="n">
+        <v>223400</v>
+      </c>
+      <c r="F34" t="n">
+        <v>223400</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4889</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46224.86627314815</v>
+      </c>
+      <c r="D35" t="n">
+        <v>719000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>719000</v>
+      </c>
+      <c r="F35" t="n">
+        <v>719000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4890</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46225.0194675926</v>
+      </c>
+      <c r="D36" t="n">
+        <v>709240</v>
+      </c>
+      <c r="E36" t="n">
+        <v>596000</v>
+      </c>
+      <c r="F36" t="n">
+        <v>596000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4893</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46225.13513888889</v>
+      </c>
+      <c r="D37" t="n">
+        <v>43000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>43000</v>
+      </c>
+      <c r="F37" t="n">
+        <v>43000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4894</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46225.14269675926</v>
+      </c>
+      <c r="D38" t="n">
+        <v>18919</v>
+      </c>
+      <c r="E38" t="n">
+        <v>18919</v>
+      </c>
+      <c r="F38" t="n">
+        <v>18919</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4895</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46225.86041666667</v>
+      </c>
+      <c r="D39" t="n">
+        <v>172669</v>
+      </c>
+      <c r="E39" t="n">
+        <v>145100</v>
+      </c>
+      <c r="F39" t="n">
+        <v>145100</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4896</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46225.95689814815</v>
+      </c>
+      <c r="D40" t="n">
+        <v>631000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>631000</v>
+      </c>
+      <c r="F40" t="n">
+        <v>631000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4897</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46226.66626157407</v>
+      </c>
+      <c r="D41" t="n">
+        <v>383900</v>
+      </c>
+      <c r="E41" t="n">
+        <v>383900</v>
+      </c>
+      <c r="F41" t="n">
+        <v>383900</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4898</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>46226.74449074074</v>
+      </c>
+      <c r="D42" t="n">
+        <v>156000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>156000</v>
+      </c>
+      <c r="F42" t="n">
+        <v>156000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4899</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46226.86318287037</v>
+      </c>
+      <c r="D43" t="n">
+        <v>57600</v>
+      </c>
+      <c r="E43" t="n">
+        <v>57600</v>
+      </c>
+      <c r="F43" t="n">
+        <v>57600</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4901</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>46226.86822916667</v>
+      </c>
+      <c r="D44" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F44" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4902</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46226.87037037037</v>
+      </c>
+      <c r="D45" t="n">
+        <v>74600</v>
+      </c>
+      <c r="E45" t="n">
+        <v>74600</v>
+      </c>
+      <c r="F45" t="n">
+        <v>74600</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4903</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46226.87275462963</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F46" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4904</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46226.93824074074</v>
+      </c>
+      <c r="D47" t="n">
+        <v>47838</v>
+      </c>
+      <c r="E47" t="n">
+        <v>40200</v>
+      </c>
+      <c r="F47" t="n">
+        <v>40200</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4905</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wc-cancelled</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46227.88310185185</v>
+      </c>
+      <c r="D48" t="n">
+        <v>49742</v>
+      </c>
+      <c r="E48" t="n">
+        <v>41800</v>
+      </c>
+      <c r="F48" t="n">
+        <v>41800</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4906</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46230.61726851852</v>
+      </c>
+      <c r="D49" t="n">
+        <v>105700</v>
+      </c>
+      <c r="E49" t="n">
+        <v>105700</v>
+      </c>
+      <c r="F49" t="n">
+        <v>105700</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4907</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46230.85891203704</v>
+      </c>
+      <c r="D50" t="n">
+        <v>39000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>39000</v>
+      </c>
+      <c r="F50" t="n">
+        <v>39000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4908</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46230.8921875</v>
+      </c>
+      <c r="D51" t="n">
+        <v>115946</v>
+      </c>
+      <c r="E51" t="n">
+        <v>115946</v>
+      </c>
+      <c r="F51" t="n">
+        <v>115946</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>4909</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46230.89417824074</v>
+      </c>
+      <c r="D52" t="n">
+        <v>89000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>89000</v>
+      </c>
+      <c r="F52" t="n">
+        <v>89000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>4910</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46230.89789351852</v>
+      </c>
+      <c r="D53" t="n">
+        <v>49500</v>
+      </c>
+      <c r="E53" t="n">
+        <v>49500</v>
+      </c>
+      <c r="F53" t="n">
+        <v>49500</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>4911</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46231.84287037037</v>
+      </c>
+      <c r="D54" t="n">
+        <v>125400</v>
+      </c>
+      <c r="E54" t="n">
+        <v>125400</v>
+      </c>
+      <c r="F54" t="n">
+        <v>125400</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4912</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46232.61981481482</v>
+      </c>
+      <c r="D55" t="n">
+        <v>73000</v>
+      </c>
+      <c r="E55" t="n">
+        <v>73000</v>
+      </c>
+      <c r="F55" t="n">
+        <v>73000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>4914</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46232.6505787037</v>
+      </c>
+      <c r="D56" t="n">
+        <v>90200</v>
+      </c>
+      <c r="E56" t="n">
+        <v>90200</v>
+      </c>
+      <c r="F56" t="n">
+        <v>90200</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>4915</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46232.65491898148</v>
+      </c>
+      <c r="D57" t="n">
+        <v>43340</v>
+      </c>
+      <c r="E57" t="n">
+        <v>43340</v>
+      </c>
+      <c r="F57" t="n">
+        <v>43340</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>4916</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46232.66456018519</v>
+      </c>
+      <c r="D58" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F58" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>4917</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>wc-pending</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46232.81538194444</v>
+      </c>
+      <c r="D59" t="n">
+        <v>179000</v>
+      </c>
+      <c r="E59" t="n">
+        <v>179000</v>
+      </c>
+      <c r="F59" t="n">
+        <v>179000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>4918</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>wc-completed</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46233.81182870371</v>
+      </c>
+      <c r="D60" t="n">
+        <v>374000</v>
+      </c>
+      <c r="E60" t="n">
+        <v>374000</v>
+      </c>
+      <c r="F60" t="n">
+        <v>374000</v>
+      </c>
+      <c r="G60" t="n">
         <v>0</v>
       </c>
     </row>
